--- a/splists_raw/ParqueMetropolitano/Copia_de_REGISTRO_DE_FLORA_DEL_PNM.xlsx
+++ b/splists_raw/ParqueMetropolitano/Copia_de_REGISTRO_DE_FLORA_DEL_PNM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07fbada46e92396b/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mullerh\Dropbox (Personal)\ForestGEO\SPLISTS\PNMplantsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{041F72B6-893F-4764-8347-D84A4A10D858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49F638F5-F1C0-4CBD-BC3D-55378C3347A0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A049DD26-845A-4F97-8AE0-F75CB776932F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BRIOFITAS" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="GIMNOSPERMAS" sheetId="3" r:id="rId3"/>
     <sheet name="MONOCOTILEDONEAS" sheetId="4" r:id="rId4"/>
     <sheet name="DICOTILEDONEAS" sheetId="6" r:id="rId5"/>
+    <sheet name="info" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1241">
   <si>
     <t>FAMILIA</t>
   </si>
@@ -5233,6 +5234,21 @@
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>Plant species list for Parque Natural Metropolitano in Panama.</t>
+  </si>
+  <si>
+    <t>Expert compiled.</t>
+  </si>
+  <si>
+    <t>Emailed by the park director, Dinora Viquez, to Helene Muller-Landau on 2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In prior conversation, Magistrada Viquez said that major contributors to this list included </t>
+  </si>
+  <si>
+    <t>Rolando Perez, Mireya Correa, and Noris Salazar (for the bryophytes)</t>
   </si>
 </sst>
 </file>
@@ -5966,15 +5982,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.53515625" customWidth="1"/>
-    <col min="2" max="2" width="37.3046875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.69140625" customWidth="1"/>
-    <col min="4" max="4" width="20.3046875" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5985,7 +6001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
         <v>359</v>
       </c>
@@ -5996,7 +6012,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53"/>
       <c r="B3" s="15" t="s">
         <v>371</v>
@@ -6005,7 +6021,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="53"/>
       <c r="B4" s="2" t="s">
         <v>372</v>
@@ -6014,7 +6030,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
       <c r="B5" s="17" t="s">
         <v>373</v>
@@ -6023,7 +6039,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>374</v>
       </c>
@@ -6034,7 +6050,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
         <v>376</v>
       </c>
@@ -6045,7 +6061,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="53"/>
       <c r="B8" s="15" t="s">
         <v>378</v>
@@ -6054,7 +6070,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="53"/>
       <c r="B9" s="15" t="s">
         <v>382</v>
@@ -6063,7 +6079,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52"/>
       <c r="B10" s="17" t="s">
         <v>383</v>
@@ -6072,7 +6088,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>380</v>
       </c>
@@ -6083,7 +6099,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>381</v>
       </c>
@@ -6094,7 +6110,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>386</v>
       </c>
@@ -6105,7 +6121,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="53"/>
       <c r="B14" s="15" t="s">
         <v>405</v>
@@ -6114,7 +6130,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="2" t="s">
         <v>404</v>
@@ -6123,7 +6139,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="53"/>
       <c r="B16" s="15" t="s">
         <v>399</v>
@@ -6132,7 +6148,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="53"/>
       <c r="B17" s="2" t="s">
         <v>400</v>
@@ -6141,7 +6157,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="53"/>
       <c r="B18" s="15" t="s">
         <v>403</v>
@@ -6150,7 +6166,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="53"/>
       <c r="B19" s="15" t="s">
         <v>401</v>
@@ -6159,7 +6175,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="53"/>
       <c r="B20" s="15" t="s">
         <v>402</v>
@@ -6168,7 +6184,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="53"/>
       <c r="B21" s="15" t="s">
         <v>406</v>
@@ -6177,7 +6193,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="53"/>
       <c r="B22" s="15" t="s">
         <v>407</v>
@@ -6186,7 +6202,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="53"/>
       <c r="B23" s="15" t="s">
         <v>408</v>
@@ -6195,7 +6211,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="53"/>
       <c r="B24" s="15" t="s">
         <v>409</v>
@@ -6204,7 +6220,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="53"/>
       <c r="B25" s="15" t="s">
         <v>411</v>
@@ -6213,7 +6229,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="53"/>
       <c r="B26" s="15" t="s">
         <v>410</v>
@@ -6222,7 +6238,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="52"/>
       <c r="B27" s="25" t="s">
         <v>412</v>
@@ -6231,7 +6247,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>440</v>
       </c>
@@ -6244,7 +6260,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>441</v>
       </c>
@@ -6255,7 +6271,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>442</v>
       </c>
@@ -6268,7 +6284,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>443</v>
       </c>
@@ -6281,7 +6297,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
         <v>444</v>
       </c>
@@ -6294,7 +6310,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="52"/>
       <c r="B33" s="17" t="s">
         <v>431</v>
@@ -6305,7 +6321,7 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>445</v>
       </c>
@@ -6318,7 +6334,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
         <v>446</v>
       </c>
@@ -6331,7 +6347,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="52"/>
       <c r="B36" s="17" t="s">
         <v>434</v>
@@ -6342,7 +6358,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="51" t="s">
         <v>447</v>
       </c>
@@ -6355,7 +6371,7 @@
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="53"/>
       <c r="B38" s="15" t="s">
         <v>436</v>
@@ -6366,7 +6382,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="52"/>
       <c r="B39" s="17" t="s">
         <v>437</v>
@@ -6377,7 +6393,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>448</v>
       </c>
@@ -6390,7 +6406,7 @@
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52"/>
       <c r="B41" s="17" t="s">
         <v>439</v>
@@ -6419,16 +6435,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.84375" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="44.3046875" customWidth="1"/>
-    <col min="4" max="4" width="20.84375" customWidth="1"/>
-    <col min="6" max="6" width="73.3046875" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="73.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6439,7 +6455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>501</v>
       </c>
@@ -6456,7 +6472,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>505</v>
       </c>
@@ -6473,7 +6489,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>506</v>
       </c>
@@ -6490,7 +6506,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>507</v>
       </c>
@@ -6507,7 +6523,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>508</v>
       </c>
@@ -6524,7 +6540,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="s">
         <v>504</v>
       </c>
@@ -6541,7 +6557,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="55"/>
       <c r="B8" t="s">
         <v>1227</v>
@@ -6556,7 +6572,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="55"/>
       <c r="B9" t="s">
         <v>465</v>
@@ -6571,7 +6587,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="55"/>
       <c r="B10" t="s">
         <v>467</v>
@@ -6586,7 +6602,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="55"/>
       <c r="B11" t="s">
         <v>457</v>
@@ -6601,7 +6617,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="55"/>
       <c r="B12" t="s">
         <v>461</v>
@@ -6616,7 +6632,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="56"/>
       <c r="B13" s="11" t="s">
         <v>459</v>
@@ -6631,7 +6647,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="54" t="s">
         <v>509</v>
       </c>
@@ -6648,7 +6664,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="55"/>
       <c r="B15" t="s">
         <v>476</v>
@@ -6663,7 +6679,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="55"/>
       <c r="B16" t="s">
         <v>478</v>
@@ -6678,7 +6694,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="55"/>
       <c r="B17" t="s">
         <v>1205</v>
@@ -6694,7 +6710,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="55"/>
       <c r="B18" t="s">
         <v>482</v>
@@ -6709,7 +6725,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="55"/>
       <c r="B19" t="s">
         <v>474</v>
@@ -6724,7 +6740,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="55"/>
       <c r="B20" t="s">
         <v>450</v>
@@ -6739,7 +6755,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="55"/>
       <c r="B21" t="s">
         <v>470</v>
@@ -6754,7 +6770,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="55"/>
       <c r="B22" t="s">
         <v>485</v>
@@ -6769,7 +6785,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="55"/>
       <c r="B23" t="s">
         <v>483</v>
@@ -6784,7 +6800,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="55"/>
       <c r="B24" t="s">
         <v>484</v>
@@ -6799,7 +6815,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="55"/>
       <c r="B25" t="s">
         <v>1190</v>
@@ -6814,7 +6830,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="55"/>
       <c r="B26" t="s">
         <v>480</v>
@@ -6829,7 +6845,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="56"/>
       <c r="B27" s="11" t="s">
         <v>472</v>
@@ -6844,7 +6860,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
         <v>1193</v>
       </c>
@@ -6861,7 +6877,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="54" t="s">
         <v>510</v>
       </c>
@@ -6878,7 +6894,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="55"/>
       <c r="B30" t="s">
         <v>487</v>
@@ -6893,7 +6909,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="56"/>
       <c r="B31" s="11" t="s">
         <v>1204</v>
@@ -6908,7 +6924,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>511</v>
       </c>
@@ -6925,7 +6941,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="54" t="s">
         <v>512</v>
       </c>
@@ -6942,7 +6958,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="55"/>
       <c r="B34" t="s">
         <v>499</v>
@@ -6957,7 +6973,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="55"/>
       <c r="B35" t="s">
         <v>497</v>
@@ -6972,7 +6988,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="55"/>
       <c r="B36" t="s">
         <v>493</v>
@@ -6987,7 +7003,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
       <c r="B37" s="11" t="s">
         <v>1203</v>
@@ -7020,13 +7036,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.3828125" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7037,7 +7053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>876</v>
       </c>
@@ -7056,15 +7072,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" customWidth="1"/>
-    <col min="2" max="2" width="46.69140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="30.84375" customWidth="1"/>
-    <col min="4" max="4" width="56.53515625" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="4" max="4" width="56.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7078,7 +7094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>3</v>
       </c>
@@ -7090,7 +7106,7 @@
       </c>
       <c r="D2" s="28"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="55"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -7100,7 +7116,7 @@
       </c>
       <c r="D3" s="29"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="55"/>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -7110,7 +7126,7 @@
       </c>
       <c r="D4" s="29"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="55"/>
       <c r="B5" s="2" t="s">
         <v>1126</v>
@@ -7120,7 +7136,7 @@
       </c>
       <c r="D5" s="29"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="55"/>
       <c r="B6" s="2" t="s">
         <v>527</v>
@@ -7132,7 +7148,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="55"/>
       <c r="B7" s="2" t="s">
         <v>561</v>
@@ -7144,7 +7160,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="55"/>
       <c r="B8" s="2" t="s">
         <v>582</v>
@@ -7154,7 +7170,7 @@
       </c>
       <c r="D8" s="29"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="55"/>
       <c r="B9" s="2" t="s">
         <v>8</v>
@@ -7164,7 +7180,7 @@
       </c>
       <c r="D9" s="29"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="55"/>
       <c r="B10" s="2" t="s">
         <v>1036</v>
@@ -7174,7 +7190,7 @@
       </c>
       <c r="D10" s="29"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="55"/>
       <c r="B11" s="2" t="s">
         <v>701</v>
@@ -7184,7 +7200,7 @@
       </c>
       <c r="D11" s="29"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="55"/>
       <c r="B12" s="2" t="s">
         <v>716</v>
@@ -7194,7 +7210,7 @@
       </c>
       <c r="D12" s="29"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="2" t="s">
         <v>10</v>
@@ -7204,7 +7220,7 @@
       </c>
       <c r="D13" s="29"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="55"/>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -7214,7 +7230,7 @@
       </c>
       <c r="D14" s="29"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="55"/>
       <c r="B15" s="2" t="s">
         <v>895</v>
@@ -7224,7 +7240,7 @@
       </c>
       <c r="D15" s="29"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="55"/>
       <c r="B16" s="2" t="s">
         <v>14</v>
@@ -7234,7 +7250,7 @@
       </c>
       <c r="D16" s="29"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="55"/>
       <c r="B17" s="2" t="s">
         <v>1128</v>
@@ -7244,7 +7260,7 @@
       </c>
       <c r="D17" s="29"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="55"/>
       <c r="B18" s="2" t="s">
         <v>859</v>
@@ -7254,7 +7270,7 @@
       </c>
       <c r="D18" s="29"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="55"/>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -7264,7 +7280,7 @@
       </c>
       <c r="D19" s="29"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="55"/>
       <c r="B20" s="2" t="s">
         <v>925</v>
@@ -7274,7 +7290,7 @@
       </c>
       <c r="D20" s="29"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="55"/>
       <c r="B21" s="2" t="s">
         <v>967</v>
@@ -7287,7 +7303,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="55"/>
       <c r="B22" s="2" t="s">
         <v>967</v>
@@ -7300,7 +7316,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="55"/>
       <c r="B23" s="2" t="s">
         <v>1129</v>
@@ -7310,7 +7326,7 @@
       </c>
       <c r="D23" s="29"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="55"/>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -7320,7 +7336,7 @@
       </c>
       <c r="D24" s="29"/>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55"/>
       <c r="B25" s="2" t="s">
         <v>17</v>
@@ -7332,7 +7348,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="54" t="s">
         <v>542</v>
       </c>
@@ -7344,7 +7360,7 @@
       </c>
       <c r="D26" s="28"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="56"/>
       <c r="B27" s="25" t="s">
         <v>1218</v>
@@ -7354,7 +7370,7 @@
       </c>
       <c r="D27" s="30"/>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
         <v>1222</v>
       </c>
@@ -7366,7 +7382,7 @@
       </c>
       <c r="D28" s="31"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
         <v>22</v>
       </c>
@@ -7380,7 +7396,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="55"/>
       <c r="B30" s="2" t="s">
         <v>19</v>
@@ -7392,7 +7408,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
       <c r="B31" s="2" t="s">
         <v>1211</v>
@@ -7402,7 +7418,7 @@
       </c>
       <c r="D31" s="29"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="55"/>
       <c r="B32" s="2" t="s">
         <v>1213</v>
@@ -7412,7 +7428,7 @@
       </c>
       <c r="D32" s="29"/>
     </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="56"/>
       <c r="B33" s="25" t="s">
         <v>1212</v>
@@ -7422,7 +7438,7 @@
       </c>
       <c r="D33" s="30"/>
     </row>
-    <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>706</v>
       </c>
@@ -7434,7 +7450,7 @@
       </c>
       <c r="D34" s="31"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="54" t="s">
         <v>23</v>
       </c>
@@ -7446,7 +7462,7 @@
       </c>
       <c r="D35" s="9"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="55"/>
       <c r="B36" s="2" t="s">
         <v>26</v>
@@ -7458,7 +7474,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="55"/>
       <c r="B37" s="2" t="s">
         <v>1130</v>
@@ -7468,7 +7484,7 @@
       </c>
       <c r="D37" s="29"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="55"/>
       <c r="B38" s="2" t="s">
         <v>28</v>
@@ -7480,7 +7496,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="55"/>
       <c r="B39" s="2" t="s">
         <v>29</v>
@@ -7490,7 +7506,7 @@
       </c>
       <c r="D39" s="10"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="55"/>
       <c r="B40" s="2" t="s">
         <v>31</v>
@@ -7500,7 +7516,7 @@
       </c>
       <c r="D40" s="10"/>
     </row>
-    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
       <c r="B41" s="25" t="s">
         <v>33</v>
@@ -7510,7 +7526,7 @@
       </c>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="54" t="s">
         <v>35</v>
       </c>
@@ -7522,7 +7538,7 @@
       </c>
       <c r="D42" s="9"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="55"/>
       <c r="B43" s="2" t="s">
         <v>614</v>
@@ -7532,7 +7548,7 @@
       </c>
       <c r="D43" s="10"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="55"/>
       <c r="B44" s="2" t="s">
         <v>38</v>
@@ -7542,7 +7558,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="55"/>
       <c r="B45" s="2" t="s">
         <v>711</v>
@@ -7552,7 +7568,7 @@
       </c>
       <c r="D45" s="10"/>
     </row>
-    <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="56"/>
       <c r="B46" s="25" t="s">
         <v>40</v>
@@ -7562,7 +7578,7 @@
       </c>
       <c r="D46" s="12"/>
     </row>
-    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>42</v>
       </c>
@@ -7574,7 +7590,7 @@
       </c>
       <c r="D47" s="27"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="54" t="s">
         <v>45</v>
       </c>
@@ -7586,7 +7602,7 @@
       </c>
       <c r="D48" s="9"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="55"/>
       <c r="B49" s="2" t="s">
         <v>1225</v>
@@ -7596,7 +7612,7 @@
       </c>
       <c r="D49" s="10"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="55"/>
       <c r="B50" s="2" t="s">
         <v>48</v>
@@ -7606,7 +7622,7 @@
       </c>
       <c r="D50" s="10"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="55"/>
       <c r="B51" s="2" t="s">
         <v>1214</v>
@@ -7616,7 +7632,7 @@
       </c>
       <c r="D51" s="10"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="55"/>
       <c r="B52" s="2" t="s">
         <v>736</v>
@@ -7626,7 +7642,7 @@
       </c>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="55"/>
       <c r="B53" s="2" t="s">
         <v>738</v>
@@ -7636,7 +7652,7 @@
       </c>
       <c r="D53" s="10"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="55"/>
       <c r="B54" s="2" t="s">
         <v>50</v>
@@ -7646,7 +7662,7 @@
       </c>
       <c r="D54" s="10"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="55"/>
       <c r="B55" s="2" t="s">
         <v>52</v>
@@ -7656,7 +7672,7 @@
       </c>
       <c r="D55" s="10"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="55"/>
       <c r="B56" s="2" t="s">
         <v>934</v>
@@ -7666,7 +7682,7 @@
       </c>
       <c r="D56" s="10"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="55"/>
       <c r="B57" s="2" t="s">
         <v>54</v>
@@ -7676,7 +7692,7 @@
       </c>
       <c r="D57" s="10"/>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="56"/>
       <c r="B58" s="25" t="s">
         <v>56</v>
@@ -7686,7 +7702,7 @@
       </c>
       <c r="D58" s="12"/>
     </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>58</v>
       </c>
@@ -7698,7 +7714,7 @@
       </c>
       <c r="D59" s="27"/>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>1016</v>
       </c>
@@ -7710,7 +7726,7 @@
       </c>
       <c r="D60" s="27"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="54" t="s">
         <v>61</v>
       </c>
@@ -7728,7 +7744,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="55"/>
       <c r="B62" s="2" t="s">
         <v>1197</v>
@@ -7744,7 +7760,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="55"/>
       <c r="B63" s="2" t="s">
         <v>64</v>
@@ -7760,7 +7776,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="55"/>
       <c r="B64" s="2" t="s">
         <v>134</v>
@@ -7773,7 +7789,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="55"/>
       <c r="B65" s="2" t="s">
         <v>66</v>
@@ -7789,7 +7805,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="56"/>
       <c r="B66" s="25" t="s">
         <v>68</v>
@@ -7805,7 +7821,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>69</v>
       </c>
@@ -7817,7 +7833,7 @@
       </c>
       <c r="D67" s="27"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="54" t="s">
         <v>72</v>
       </c>
@@ -7829,7 +7845,7 @@
       </c>
       <c r="D68" s="9"/>
     </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="56"/>
       <c r="B69" s="25" t="s">
         <v>1132</v>
@@ -7839,7 +7855,7 @@
       </c>
       <c r="D69" s="12"/>
     </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>811</v>
       </c>
@@ -7851,7 +7867,7 @@
       </c>
       <c r="D70" s="27"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="54" t="s">
         <v>75</v>
       </c>
@@ -7869,7 +7885,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="55"/>
       <c r="B72" s="2" t="s">
         <v>77</v>
@@ -7879,7 +7895,7 @@
       </c>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="55"/>
       <c r="B73" s="2" t="s">
         <v>90</v>
@@ -7889,7 +7905,7 @@
       </c>
       <c r="D73" s="10"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="55"/>
       <c r="B74" s="2" t="s">
         <v>78</v>
@@ -7899,7 +7915,7 @@
       </c>
       <c r="D74" s="10"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="55"/>
       <c r="B75" s="2" t="s">
         <v>1185</v>
@@ -7915,7 +7931,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="55"/>
       <c r="B76" s="2" t="s">
         <v>79</v>
@@ -7925,7 +7941,7 @@
       </c>
       <c r="D76" s="10"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="55"/>
       <c r="B77" s="2" t="s">
         <v>80</v>
@@ -7935,7 +7951,7 @@
       </c>
       <c r="D77" s="10"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="55"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -7945,7 +7961,7 @@
       </c>
       <c r="D78" s="10"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="55"/>
       <c r="B79" s="2" t="s">
         <v>82</v>
@@ -7955,7 +7971,7 @@
       </c>
       <c r="D79" s="10"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="55"/>
       <c r="B80" s="2" t="s">
         <v>101</v>
@@ -7971,7 +7987,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="55"/>
       <c r="B81" s="2" t="s">
         <v>1207</v>
@@ -7987,7 +8003,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="55"/>
       <c r="B82" s="2" t="s">
         <v>91</v>
@@ -8003,7 +8019,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="55"/>
       <c r="B83" s="2" t="s">
         <v>98</v>
@@ -8019,7 +8035,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="55"/>
       <c r="B84" s="2" t="s">
         <v>83</v>
@@ -8029,7 +8045,7 @@
       </c>
       <c r="D84" s="10"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="55"/>
       <c r="B85" s="2" t="s">
         <v>1189</v>
@@ -8045,7 +8061,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="55"/>
       <c r="B86" s="2" t="s">
         <v>84</v>
@@ -8055,7 +8071,7 @@
       </c>
       <c r="D86" s="10"/>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="56"/>
       <c r="B87" s="25" t="s">
         <v>85</v>
@@ -8065,7 +8081,7 @@
       </c>
       <c r="D87" s="12"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>878</v>
       </c>
@@ -8075,7 +8091,7 @@
       <c r="C88" s="26"/>
       <c r="D88" s="27"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="54" t="s">
         <v>103</v>
       </c>
@@ -8087,7 +8103,7 @@
       </c>
       <c r="D89" s="9"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="55"/>
       <c r="B90" s="2" t="s">
         <v>104</v>
@@ -8097,7 +8113,7 @@
       </c>
       <c r="D90" s="10"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="55"/>
       <c r="B91" s="2" t="s">
         <v>106</v>
@@ -8107,7 +8123,7 @@
       </c>
       <c r="D91" s="10"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="55"/>
       <c r="B92" s="2" t="s">
         <v>108</v>
@@ -8117,7 +8133,7 @@
       </c>
       <c r="D92" s="10"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="55"/>
       <c r="B93" s="2" t="s">
         <v>110</v>
@@ -8127,7 +8143,7 @@
       </c>
       <c r="D93" s="10"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="55"/>
       <c r="B94" s="2" t="s">
         <v>112</v>
@@ -8137,7 +8153,7 @@
       </c>
       <c r="D94" s="10"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="55"/>
       <c r="B95" s="2" t="s">
         <v>113</v>
@@ -8149,7 +8165,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="55"/>
       <c r="B96" s="2" t="s">
         <v>115</v>
@@ -8159,7 +8175,7 @@
       </c>
       <c r="D96" s="10"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="55"/>
       <c r="B97" s="2" t="s">
         <v>116</v>
@@ -8169,7 +8185,7 @@
       </c>
       <c r="D97" s="10"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="55"/>
       <c r="B98" s="2" t="s">
         <v>118</v>
@@ -8179,7 +8195,7 @@
       </c>
       <c r="D98" s="10"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="55"/>
       <c r="B99" s="2" t="s">
         <v>1133</v>
@@ -8189,7 +8205,7 @@
       </c>
       <c r="D99" s="10"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="55"/>
       <c r="B100" s="2" t="s">
         <v>120</v>
@@ -8199,7 +8215,7 @@
       </c>
       <c r="D100" s="10"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="55"/>
       <c r="B101" s="2" t="s">
         <v>121</v>
@@ -8209,7 +8225,7 @@
       </c>
       <c r="D101" s="10"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="55"/>
       <c r="B102" s="2" t="s">
         <v>123</v>
@@ -8219,7 +8235,7 @@
       </c>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="55"/>
       <c r="B103" s="2" t="s">
         <v>125</v>
@@ -8229,7 +8245,7 @@
       </c>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="55"/>
       <c r="B104" s="2" t="s">
         <v>126</v>
@@ -8239,7 +8255,7 @@
       </c>
       <c r="D104" s="10"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="55"/>
       <c r="B105" s="2" t="s">
         <v>128</v>
@@ -8249,7 +8265,7 @@
       </c>
       <c r="D105" s="10"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="55"/>
       <c r="B106" s="2" t="s">
         <v>974</v>
@@ -8259,7 +8275,7 @@
       </c>
       <c r="D106" s="10"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="55"/>
       <c r="B107" s="2" t="s">
         <v>130</v>
@@ -8269,7 +8285,7 @@
       </c>
       <c r="D107" s="10"/>
     </row>
-    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="56"/>
       <c r="B108" s="25" t="s">
         <v>1134</v>
@@ -8281,7 +8297,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>1137</v>
       </c>
@@ -8293,7 +8309,7 @@
       </c>
       <c r="D109" s="31"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="54" t="s">
         <v>131</v>
       </c>
@@ -8305,7 +8321,7 @@
       </c>
       <c r="D110" s="9"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="55"/>
       <c r="B111" s="2" t="s">
         <v>521</v>
@@ -8315,7 +8331,7 @@
       </c>
       <c r="D111" s="10"/>
     </row>
-    <row r="112" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="56"/>
       <c r="B112" s="25" t="s">
         <v>132</v>
@@ -8347,16 +8363,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E447"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.53515625" customWidth="1"/>
-    <col min="2" max="2" width="31.84375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.84375" customWidth="1"/>
-    <col min="4" max="4" width="29.84375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.15234375" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>1235</v>
       </c>
@@ -8370,7 +8386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>136</v>
       </c>
@@ -8382,7 +8398,7 @@
       </c>
       <c r="D2" s="41"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="35" t="s">
         <v>137</v>
@@ -8392,7 +8408,7 @@
       </c>
       <c r="D3" s="41"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49"/>
       <c r="B4" s="35" t="s">
         <v>139</v>
@@ -8402,7 +8418,7 @@
       </c>
       <c r="D4" s="41"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49"/>
       <c r="B5" s="35" t="s">
         <v>141</v>
@@ -8412,7 +8428,7 @@
       </c>
       <c r="D5" s="41"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49"/>
       <c r="B6" s="35" t="s">
         <v>144</v>
@@ -8422,7 +8438,7 @@
       </c>
       <c r="D6" s="41"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49"/>
       <c r="B7" s="35" t="s">
         <v>145</v>
@@ -8432,7 +8448,7 @@
       </c>
       <c r="D7" s="41"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49"/>
       <c r="B8" s="35" t="s">
         <v>146</v>
@@ -8442,7 +8458,7 @@
       </c>
       <c r="D8" s="41"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="49"/>
       <c r="B9" s="35" t="s">
         <v>147</v>
@@ -8452,7 +8468,7 @@
       </c>
       <c r="D9" s="41"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="49"/>
       <c r="B10" s="35" t="s">
         <v>149</v>
@@ -8462,7 +8478,7 @@
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
         <v>802</v>
       </c>
@@ -8474,7 +8490,7 @@
       </c>
       <c r="D11" s="41"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="49" t="s">
         <v>151</v>
       </c>
@@ -8486,7 +8502,7 @@
       </c>
       <c r="D12" s="41"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="49"/>
       <c r="B13" s="35" t="s">
         <v>153</v>
@@ -8496,7 +8512,7 @@
       </c>
       <c r="D13" s="41"/>
     </row>
-    <row r="14" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
         <v>554</v>
       </c>
@@ -8510,7 +8526,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="49"/>
       <c r="B15" s="35" t="s">
         <v>555</v>
@@ -8520,7 +8536,7 @@
       </c>
       <c r="D15" s="41"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="49"/>
       <c r="B16" s="35" t="s">
         <v>553</v>
@@ -8530,7 +8546,7 @@
       </c>
       <c r="D16" s="41"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="49"/>
       <c r="B17" s="35" t="s">
         <v>808</v>
@@ -8540,7 +8556,7 @@
       </c>
       <c r="D17" s="41"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="49"/>
       <c r="B18" s="35" t="s">
         <v>957</v>
@@ -8550,7 +8566,7 @@
       </c>
       <c r="D18" s="41"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="49"/>
       <c r="B19" s="35" t="s">
         <v>958</v>
@@ -8563,7 +8579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="49" t="s">
         <v>513</v>
       </c>
@@ -8575,7 +8591,7 @@
       </c>
       <c r="D20" s="41"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="49"/>
       <c r="B21" s="35" t="s">
         <v>518</v>
@@ -8585,7 +8601,7 @@
       </c>
       <c r="D21" s="41"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="49"/>
       <c r="B22" s="35" t="s">
         <v>1030</v>
@@ -8595,7 +8611,7 @@
       </c>
       <c r="D22" s="41"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="49"/>
       <c r="B23" s="35" t="s">
         <v>514</v>
@@ -8605,7 +8621,7 @@
       </c>
       <c r="D23" s="41"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="49"/>
       <c r="B24" s="35" t="s">
         <v>1018</v>
@@ -8615,7 +8631,7 @@
       </c>
       <c r="D24" s="41"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="49"/>
       <c r="B25" s="35" t="s">
         <v>1020</v>
@@ -8625,7 +8641,7 @@
       </c>
       <c r="D25" s="41"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
         <v>734</v>
       </c>
@@ -8637,7 +8653,7 @@
       </c>
       <c r="D26" s="41"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
       <c r="B27" s="35" t="s">
         <v>763</v>
@@ -8647,7 +8663,7 @@
       </c>
       <c r="D27" s="41"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49" t="s">
         <v>155</v>
       </c>
@@ -8659,7 +8675,7 @@
       </c>
       <c r="D28" s="41"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="49"/>
       <c r="B29" s="35" t="s">
         <v>530</v>
@@ -8669,7 +8685,7 @@
       </c>
       <c r="D29" s="41"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
       <c r="B30" s="35" t="s">
         <v>699</v>
@@ -8679,7 +8695,7 @@
       </c>
       <c r="D30" s="41"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="49"/>
       <c r="B31" s="35" t="s">
         <v>156</v>
@@ -8689,7 +8705,7 @@
       </c>
       <c r="D31" s="41"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
       <c r="B32" s="35" t="s">
         <v>158</v>
@@ -8701,7 +8717,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
       <c r="B33" s="35" t="s">
         <v>746</v>
@@ -8711,7 +8727,7 @@
       </c>
       <c r="D33" s="41"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
       <c r="B34" s="35" t="s">
         <v>1031</v>
@@ -8721,7 +8737,7 @@
       </c>
       <c r="D34" s="41"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="49"/>
       <c r="B35" s="35" t="s">
         <v>160</v>
@@ -8733,7 +8749,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="35" t="s">
         <v>162</v>
@@ -8745,7 +8761,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="49"/>
       <c r="B37" s="35" t="s">
         <v>1141</v>
@@ -8755,7 +8771,7 @@
       </c>
       <c r="D37" s="41"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="35" t="s">
         <v>164</v>
@@ -8765,7 +8781,7 @@
       </c>
       <c r="D38" s="41"/>
     </row>
-    <row r="39" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="35" t="s">
         <v>166</v>
@@ -8777,7 +8793,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="35" t="s">
         <v>1143</v>
@@ -8787,7 +8803,7 @@
       </c>
       <c r="D40" s="41"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="49"/>
       <c r="B41" s="35" t="s">
         <v>1144</v>
@@ -8797,7 +8813,7 @@
       </c>
       <c r="D41" s="41"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="35" t="s">
         <v>168</v>
@@ -8807,7 +8823,7 @@
       </c>
       <c r="D42" s="41"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="49"/>
       <c r="B43" s="35" t="s">
         <v>1033</v>
@@ -8817,7 +8833,7 @@
       </c>
       <c r="D43" s="41"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="49"/>
       <c r="B44" s="35" t="s">
         <v>170</v>
@@ -8829,7 +8845,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="49"/>
       <c r="B45" s="35" t="s">
         <v>927</v>
@@ -8839,7 +8855,7 @@
       </c>
       <c r="D45" s="41"/>
     </row>
-    <row r="46" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="49"/>
       <c r="B46" s="35" t="s">
         <v>959</v>
@@ -8851,7 +8867,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="49"/>
       <c r="B47" s="35" t="s">
         <v>988</v>
@@ -8861,7 +8877,7 @@
       </c>
       <c r="D47" s="41"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="49" t="s">
         <v>720</v>
       </c>
@@ -8873,7 +8889,7 @@
       </c>
       <c r="D48" s="41"/>
     </row>
-    <row r="49" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="49"/>
       <c r="B49" s="35" t="s">
         <v>962</v>
@@ -8883,7 +8899,7 @@
       </c>
       <c r="D49" s="41"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="49"/>
       <c r="B50" s="35" t="s">
         <v>1035</v>
@@ -8893,7 +8909,7 @@
       </c>
       <c r="D50" s="41"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="49" t="s">
         <v>172</v>
       </c>
@@ -8905,7 +8921,7 @@
       </c>
       <c r="D51" s="41"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="49"/>
       <c r="B52" s="35" t="s">
         <v>174</v>
@@ -8917,7 +8933,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="49"/>
       <c r="B53" s="35" t="s">
         <v>534</v>
@@ -8927,7 +8943,7 @@
       </c>
       <c r="D53" s="41"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="49" t="s">
         <v>175</v>
       </c>
@@ -8939,7 +8955,7 @@
       </c>
       <c r="D54" s="41"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="49"/>
       <c r="B55" s="35" t="s">
         <v>570</v>
@@ -8949,7 +8965,7 @@
       </c>
       <c r="D55" s="41"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="49"/>
       <c r="B56" s="35" t="s">
         <v>176</v>
@@ -8959,7 +8975,7 @@
       </c>
       <c r="D56" s="41"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="49"/>
       <c r="B57" s="35" t="s">
         <v>1147</v>
@@ -8969,7 +8985,7 @@
       </c>
       <c r="D57" s="41"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="49"/>
       <c r="B58" s="35" t="s">
         <v>178</v>
@@ -8979,7 +8995,7 @@
       </c>
       <c r="D58" s="41"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="49"/>
       <c r="B59" s="35" t="s">
         <v>180</v>
@@ -8989,7 +9005,7 @@
       </c>
       <c r="D59" s="41"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="49"/>
       <c r="B60" s="35" t="s">
         <v>182</v>
@@ -8999,13 +9015,13 @@
       </c>
       <c r="D60" s="41"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="49"/>
       <c r="B61" s="35"/>
       <c r="C61" s="36"/>
       <c r="D61" s="41"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="49"/>
       <c r="B62" s="35" t="s">
         <v>184</v>
@@ -9017,7 +9033,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="49"/>
       <c r="B63" s="35" t="s">
         <v>186</v>
@@ -9027,7 +9043,7 @@
       </c>
       <c r="D63" s="41"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="49"/>
       <c r="B64" s="35" t="s">
         <v>188</v>
@@ -9039,7 +9055,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="49"/>
       <c r="B65" s="35" t="s">
         <v>765</v>
@@ -9051,7 +9067,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="49"/>
       <c r="B66" s="35" t="s">
         <v>766</v>
@@ -9061,7 +9077,7 @@
       </c>
       <c r="D66" s="41"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="49"/>
       <c r="B67" s="35" t="s">
         <v>844</v>
@@ -9071,7 +9087,7 @@
       </c>
       <c r="D67" s="41"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="49"/>
       <c r="B68" s="35" t="s">
         <v>191</v>
@@ -9081,7 +9097,7 @@
       </c>
       <c r="D68" s="41"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="49"/>
       <c r="B69" s="35" t="s">
         <v>1148</v>
@@ -9091,7 +9107,7 @@
       </c>
       <c r="D69" s="41"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="49"/>
       <c r="B70" s="35" t="s">
         <v>936</v>
@@ -9101,7 +9117,7 @@
       </c>
       <c r="D70" s="41"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="49"/>
       <c r="B71" s="35" t="s">
         <v>1149</v>
@@ -9111,7 +9127,7 @@
       </c>
       <c r="D71" s="41"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="49"/>
       <c r="B72" s="35" t="s">
         <v>1150</v>
@@ -9121,7 +9137,7 @@
       </c>
       <c r="D72" s="41"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="49"/>
       <c r="B73" s="35" t="s">
         <v>764</v>
@@ -9133,7 +9149,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="49"/>
       <c r="B74" s="35" t="s">
         <v>987</v>
@@ -9143,7 +9159,7 @@
       </c>
       <c r="D74" s="41"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="49"/>
       <c r="B75" s="35" t="s">
         <v>1010</v>
@@ -9153,7 +9169,7 @@
       </c>
       <c r="D75" s="41"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="49"/>
       <c r="B76" s="35" t="s">
         <v>1151</v>
@@ -9163,7 +9179,7 @@
       </c>
       <c r="D76" s="41"/>
     </row>
-    <row r="77" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="49" t="s">
         <v>194</v>
       </c>
@@ -9177,7 +9193,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="49"/>
       <c r="B78" s="35" t="s">
         <v>197</v>
@@ -9187,7 +9203,7 @@
       </c>
       <c r="D78" s="41"/>
     </row>
-    <row r="79" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="49"/>
       <c r="B79" s="35" t="s">
         <v>199</v>
@@ -9199,7 +9215,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="49"/>
       <c r="B80" s="35" t="s">
         <v>201</v>
@@ -9209,7 +9225,7 @@
       </c>
       <c r="D80" s="41"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="49"/>
       <c r="B81" s="35" t="s">
         <v>1037</v>
@@ -9219,7 +9235,7 @@
       </c>
       <c r="D81" s="41"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="49"/>
       <c r="B82" s="35" t="s">
         <v>203</v>
@@ -9231,7 +9247,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="49"/>
       <c r="B83" s="35" t="s">
         <v>204</v>
@@ -9243,7 +9259,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="49"/>
       <c r="B84" s="35" t="s">
         <v>206</v>
@@ -9255,7 +9271,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="49"/>
       <c r="B85" s="35" t="s">
         <v>751</v>
@@ -9265,7 +9281,7 @@
       </c>
       <c r="D85" s="41"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="49"/>
       <c r="B86" s="35" t="s">
         <v>1039</v>
@@ -9277,7 +9293,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="49"/>
       <c r="B87" s="35" t="s">
         <v>208</v>
@@ -9289,7 +9305,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="49"/>
       <c r="B88" s="35" t="s">
         <v>1152</v>
@@ -9301,7 +9317,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="49"/>
       <c r="B89" s="35" t="s">
         <v>975</v>
@@ -9311,7 +9327,7 @@
       </c>
       <c r="D89" s="41"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="49"/>
       <c r="B90" s="35" t="s">
         <v>210</v>
@@ -9321,7 +9337,7 @@
       </c>
       <c r="D90" s="41"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="49"/>
       <c r="B91" s="35" t="s">
         <v>998</v>
@@ -9331,7 +9347,7 @@
       </c>
       <c r="D91" s="41"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="49"/>
       <c r="B92" s="35" t="s">
         <v>212</v>
@@ -9341,7 +9357,7 @@
       </c>
       <c r="D92" s="41"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="49" t="s">
         <v>584</v>
       </c>
@@ -9353,7 +9369,7 @@
       </c>
       <c r="D93" s="41"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="49"/>
       <c r="B94" s="35" t="s">
         <v>696</v>
@@ -9363,7 +9379,7 @@
       </c>
       <c r="D94" s="41"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="49" t="s">
         <v>1041</v>
       </c>
@@ -9375,7 +9391,7 @@
       </c>
       <c r="D95" s="41"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="49"/>
       <c r="B96" s="35" t="s">
         <v>653</v>
@@ -9385,7 +9401,7 @@
       </c>
       <c r="D96" s="41"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="42" t="s">
         <v>579</v>
       </c>
@@ -9397,7 +9413,7 @@
       </c>
       <c r="D97" s="41"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="49" t="s">
         <v>781</v>
       </c>
@@ -9409,7 +9425,7 @@
       </c>
       <c r="D98" s="41"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="49"/>
       <c r="B99" s="35" t="s">
         <v>1199</v>
@@ -9424,7 +9440,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="49"/>
       <c r="B100" s="35" t="s">
         <v>879</v>
@@ -9434,7 +9450,7 @@
       </c>
       <c r="D100" s="41"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="42" t="s">
         <v>589</v>
       </c>
@@ -9446,7 +9462,7 @@
       </c>
       <c r="D101" s="41"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="42" t="s">
         <v>1155</v>
       </c>
@@ -9458,7 +9474,7 @@
       </c>
       <c r="D102" s="41"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="49" t="s">
         <v>703</v>
       </c>
@@ -9470,7 +9486,7 @@
       </c>
       <c r="D103" s="41"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="49"/>
       <c r="B104" s="35" t="s">
         <v>1233</v>
@@ -9480,7 +9496,7 @@
       </c>
       <c r="D104" s="41"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="42" t="s">
         <v>658</v>
       </c>
@@ -9492,7 +9508,7 @@
       </c>
       <c r="D105" s="41"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="42" t="s">
         <v>685</v>
       </c>
@@ -9504,7 +9520,7 @@
       </c>
       <c r="D106" s="41"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="49" t="s">
         <v>214</v>
       </c>
@@ -9516,7 +9532,7 @@
       </c>
       <c r="D107" s="41"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="49"/>
       <c r="B108" s="35" t="s">
         <v>215</v>
@@ -9526,7 +9542,7 @@
       </c>
       <c r="D108" s="41"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="49"/>
       <c r="B109" s="35" t="s">
         <v>217</v>
@@ -9536,7 +9552,7 @@
       </c>
       <c r="D109" s="41"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="49" t="s">
         <v>782</v>
       </c>
@@ -9548,7 +9564,7 @@
       </c>
       <c r="D110" s="41"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="49"/>
       <c r="B111" s="35" t="s">
         <v>784</v>
@@ -9558,7 +9574,7 @@
       </c>
       <c r="D111" s="41"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="49"/>
       <c r="B112" s="35" t="s">
         <v>792</v>
@@ -9568,7 +9584,7 @@
       </c>
       <c r="D112" s="41"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="50" t="s">
         <v>1157</v>
       </c>
@@ -9580,7 +9596,7 @@
       </c>
       <c r="D113" s="41"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="50"/>
       <c r="B114" s="35" t="s">
         <v>1160</v>
@@ -9590,7 +9606,7 @@
       </c>
       <c r="D114" s="41"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="42" t="s">
         <v>693</v>
       </c>
@@ -9602,7 +9618,7 @@
       </c>
       <c r="D115" s="41"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="49" t="s">
         <v>221</v>
       </c>
@@ -9612,7 +9628,7 @@
       <c r="C116" s="36"/>
       <c r="D116" s="41"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="49"/>
       <c r="B117" s="35" t="s">
         <v>219</v>
@@ -9624,7 +9640,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="49"/>
       <c r="B118" s="35" t="s">
         <v>980</v>
@@ -9636,7 +9652,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="49"/>
       <c r="B119" s="35" t="s">
         <v>1045</v>
@@ -9646,7 +9662,7 @@
       </c>
       <c r="D119" s="41"/>
     </row>
-    <row r="120" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="49"/>
       <c r="B120" s="35" t="s">
         <v>983</v>
@@ -9658,7 +9674,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="49" t="s">
         <v>624</v>
       </c>
@@ -9670,7 +9686,7 @@
       </c>
       <c r="D121" s="41"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="49"/>
       <c r="B122" s="35" t="s">
         <v>1046</v>
@@ -9680,7 +9696,7 @@
       </c>
       <c r="D122" s="41"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="49" t="s">
         <v>222</v>
       </c>
@@ -9692,7 +9708,7 @@
       </c>
       <c r="D123" s="41"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="49"/>
       <c r="B124" s="35" t="s">
         <v>224</v>
@@ -9702,7 +9718,7 @@
       </c>
       <c r="D124" s="41"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="49"/>
       <c r="B125" s="35" t="s">
         <v>1162</v>
@@ -9712,7 +9728,7 @@
       </c>
       <c r="D125" s="41"/>
     </row>
-    <row r="126" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="49"/>
       <c r="B126" s="35" t="s">
         <v>226</v>
@@ -9724,7 +9740,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="49"/>
       <c r="B127" s="35" t="s">
         <v>1164</v>
@@ -9736,7 +9752,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="49" t="s">
         <v>228</v>
       </c>
@@ -9748,7 +9764,7 @@
       </c>
       <c r="D128" s="41"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="49"/>
       <c r="B129" s="35" t="s">
         <v>1048</v>
@@ -9758,7 +9774,7 @@
       </c>
       <c r="D129" s="41"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="49"/>
       <c r="B130" s="35" t="s">
         <v>830</v>
@@ -9768,7 +9784,7 @@
       </c>
       <c r="D130" s="41"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="49"/>
       <c r="B131" s="35" t="s">
         <v>230</v>
@@ -9778,7 +9794,7 @@
       </c>
       <c r="D131" s="41"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="49"/>
       <c r="B132" s="35" t="s">
         <v>839</v>
@@ -9788,7 +9804,7 @@
       </c>
       <c r="D132" s="41"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="49"/>
       <c r="B133" s="35" t="s">
         <v>231</v>
@@ -9798,7 +9814,7 @@
       </c>
       <c r="D133" s="41"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="49"/>
       <c r="B134" s="35" t="s">
         <v>233</v>
@@ -9808,7 +9824,7 @@
       </c>
       <c r="D134" s="41"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="49" t="s">
         <v>1049</v>
       </c>
@@ -9820,7 +9836,7 @@
       </c>
       <c r="D135" s="41"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="49"/>
       <c r="B136" s="35" t="s">
         <v>1050</v>
@@ -9830,7 +9846,7 @@
       </c>
       <c r="D136" s="41"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="49"/>
       <c r="B137" s="35" t="s">
         <v>235</v>
@@ -9840,7 +9856,7 @@
       </c>
       <c r="D137" s="41"/>
     </row>
-    <row r="138" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="49"/>
       <c r="B138" s="35" t="s">
         <v>718</v>
@@ -9850,7 +9866,7 @@
       </c>
       <c r="D138" s="41"/>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="49"/>
       <c r="B139" s="35" t="s">
         <v>1052</v>
@@ -9860,7 +9876,7 @@
       </c>
       <c r="D139" s="41"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="49"/>
       <c r="B140" s="35" t="s">
         <v>1167</v>
@@ -9870,7 +9886,7 @@
       </c>
       <c r="D140" s="41"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="42" t="s">
         <v>943</v>
       </c>
@@ -9882,7 +9898,7 @@
       </c>
       <c r="D141" s="44"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="49" t="s">
         <v>237</v>
       </c>
@@ -9894,7 +9910,7 @@
       </c>
       <c r="D142" s="41"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="49"/>
       <c r="B143" s="35" t="s">
         <v>239</v>
@@ -9904,7 +9920,7 @@
       </c>
       <c r="D143" s="41"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="49"/>
       <c r="B144" s="35" t="s">
         <v>546</v>
@@ -9914,7 +9930,7 @@
       </c>
       <c r="D144" s="41"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="49"/>
       <c r="B145" s="35" t="s">
         <v>666</v>
@@ -9926,7 +9942,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="49"/>
       <c r="B146" s="35" t="s">
         <v>665</v>
@@ -9936,7 +9952,7 @@
       </c>
       <c r="D146" s="41"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="49"/>
       <c r="B147" s="35" t="s">
         <v>607</v>
@@ -9946,7 +9962,7 @@
       </c>
       <c r="D147" s="41"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="49"/>
       <c r="B148" s="35" t="s">
         <v>241</v>
@@ -9956,7 +9972,7 @@
       </c>
       <c r="D148" s="41"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="49"/>
       <c r="B149" s="35" t="s">
         <v>1168</v>
@@ -9966,7 +9982,7 @@
       </c>
       <c r="D149" s="41"/>
     </row>
-    <row r="150" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="49"/>
       <c r="B150" s="35" t="s">
         <v>769</v>
@@ -9978,7 +9994,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="49"/>
       <c r="B151" s="35" t="s">
         <v>242</v>
@@ -9990,7 +10006,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="49"/>
       <c r="B152" s="35" t="s">
         <v>603</v>
@@ -10002,7 +10018,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="49"/>
       <c r="B153" s="35" t="s">
         <v>606</v>
@@ -10014,7 +10030,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="49"/>
       <c r="B154" s="35" t="s">
         <v>778</v>
@@ -10024,7 +10040,7 @@
       </c>
       <c r="D154" s="41"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="49"/>
       <c r="B155" s="35" t="s">
         <v>809</v>
@@ -10034,7 +10050,7 @@
       </c>
       <c r="D155" s="41"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="49"/>
       <c r="B156" s="35" t="s">
         <v>1053</v>
@@ -10044,7 +10060,7 @@
       </c>
       <c r="D156" s="41"/>
     </row>
-    <row r="157" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="49" t="s">
         <v>243</v>
       </c>
@@ -10058,7 +10074,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="49"/>
       <c r="B158" s="35" t="s">
         <v>1055</v>
@@ -10070,7 +10086,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="49"/>
       <c r="B159" s="35" t="s">
         <v>1057</v>
@@ -10078,7 +10094,7 @@
       <c r="C159" s="36"/>
       <c r="D159" s="41"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="49"/>
       <c r="B160" s="35" t="s">
         <v>526</v>
@@ -10088,7 +10104,7 @@
       </c>
       <c r="D160" s="41"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="49"/>
       <c r="B161" s="35" t="s">
         <v>524</v>
@@ -10098,7 +10114,7 @@
       </c>
       <c r="D161" s="41"/>
     </row>
-    <row r="162" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="49"/>
       <c r="B162" s="35" t="s">
         <v>548</v>
@@ -10108,7 +10124,7 @@
       </c>
       <c r="D162" s="41"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="49"/>
       <c r="B163" s="35" t="s">
         <v>1058</v>
@@ -10118,7 +10134,7 @@
       </c>
       <c r="D163" s="41"/>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="49"/>
       <c r="B164" s="35" t="s">
         <v>1169</v>
@@ -10128,7 +10144,7 @@
       </c>
       <c r="D164" s="41"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="49"/>
       <c r="B165" s="35" t="s">
         <v>550</v>
@@ -10140,7 +10156,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="49"/>
       <c r="B166" s="35" t="s">
         <v>587</v>
@@ -10150,7 +10166,7 @@
       </c>
       <c r="D166" s="41"/>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="49"/>
       <c r="B167" s="35" t="s">
         <v>567</v>
@@ -10160,7 +10176,7 @@
       </c>
       <c r="D167" s="41"/>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="49"/>
       <c r="B168" s="35" t="s">
         <v>585</v>
@@ -10170,7 +10186,7 @@
       </c>
       <c r="D168" s="41"/>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="49"/>
       <c r="B169" s="35" t="s">
         <v>592</v>
@@ -10180,7 +10196,7 @@
       </c>
       <c r="D169" s="41"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="49"/>
       <c r="B170" s="35" t="s">
         <v>246</v>
@@ -10190,7 +10206,7 @@
       </c>
       <c r="D170" s="41"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="49"/>
       <c r="B171" s="35" t="s">
         <v>1170</v>
@@ -10200,7 +10216,7 @@
       </c>
       <c r="D171" s="41"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="49"/>
       <c r="B172" s="35" t="s">
         <v>248</v>
@@ -10210,7 +10226,7 @@
       </c>
       <c r="D172" s="41"/>
     </row>
-    <row r="173" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="49"/>
       <c r="B173" s="35" t="s">
         <v>596</v>
@@ -10222,7 +10238,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="49"/>
       <c r="B174" s="35" t="s">
         <v>250</v>
@@ -10232,7 +10248,7 @@
       </c>
       <c r="D174" s="41"/>
     </row>
-    <row r="175" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="49"/>
       <c r="B175" s="35" t="s">
         <v>1060</v>
@@ -10244,7 +10260,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="49"/>
       <c r="B176" s="35" t="s">
         <v>676</v>
@@ -10254,7 +10270,7 @@
       </c>
       <c r="D176" s="41"/>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="49"/>
       <c r="B177" s="35" t="s">
         <v>678</v>
@@ -10264,7 +10280,7 @@
       </c>
       <c r="D177" s="41"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="49"/>
       <c r="B178" s="35" t="s">
         <v>609</v>
@@ -10274,7 +10290,7 @@
       </c>
       <c r="D178" s="41"/>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="49"/>
       <c r="B179" s="35" t="s">
         <v>713</v>
@@ -10284,7 +10300,7 @@
       </c>
       <c r="D179" s="41"/>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="49"/>
       <c r="B180" s="35" t="s">
         <v>709</v>
@@ -10294,7 +10310,7 @@
       </c>
       <c r="D180" s="41"/>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="49"/>
       <c r="B181" s="35" t="s">
         <v>252</v>
@@ -10304,7 +10320,7 @@
       </c>
       <c r="D181" s="41"/>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="49"/>
       <c r="B182" s="35" t="s">
         <v>1171</v>
@@ -10314,7 +10330,7 @@
       </c>
       <c r="D182" s="41"/>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="49"/>
       <c r="B183" s="35" t="s">
         <v>1173</v>
@@ -10324,7 +10340,7 @@
       </c>
       <c r="D183" s="41"/>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="49"/>
       <c r="B184" s="35" t="s">
         <v>1063</v>
@@ -10334,7 +10350,7 @@
       </c>
       <c r="D184" s="41"/>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="49"/>
       <c r="B185" s="35" t="s">
         <v>714</v>
@@ -10344,7 +10360,7 @@
       </c>
       <c r="D185" s="41"/>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="49"/>
       <c r="B186" s="35" t="s">
         <v>710</v>
@@ -10354,7 +10370,7 @@
       </c>
       <c r="D186" s="41"/>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="49"/>
       <c r="B187" s="35" t="s">
         <v>724</v>
@@ -10364,7 +10380,7 @@
       </c>
       <c r="D187" s="41"/>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="49"/>
       <c r="B188" s="35" t="s">
         <v>726</v>
@@ -10374,7 +10390,7 @@
       </c>
       <c r="D188" s="41"/>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="49"/>
       <c r="B189" s="35" t="s">
         <v>728</v>
@@ -10384,7 +10400,7 @@
       </c>
       <c r="D189" s="41"/>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="49"/>
       <c r="B190" s="35" t="s">
         <v>730</v>
@@ -10394,7 +10410,7 @@
       </c>
       <c r="D190" s="41"/>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="49"/>
       <c r="B191" s="35" t="s">
         <v>732</v>
@@ -10404,7 +10420,7 @@
       </c>
       <c r="D191" s="41"/>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="49"/>
       <c r="B192" s="35" t="s">
         <v>1064</v>
@@ -10414,7 +10430,7 @@
       </c>
       <c r="D192" s="41"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="49"/>
       <c r="B193" s="35" t="s">
         <v>741</v>
@@ -10424,7 +10440,7 @@
       </c>
       <c r="D193" s="41"/>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="49"/>
       <c r="B194" s="35" t="s">
         <v>1065</v>
@@ -10436,7 +10452,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="49"/>
       <c r="B195" s="35" t="s">
         <v>1068</v>
@@ -10446,7 +10462,7 @@
       </c>
       <c r="D195" s="41"/>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="49"/>
       <c r="B196" s="35" t="s">
         <v>1174</v>
@@ -10456,7 +10472,7 @@
       </c>
       <c r="D196" s="41"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="49"/>
       <c r="B197" s="35" t="s">
         <v>785</v>
@@ -10466,7 +10482,7 @@
       </c>
       <c r="D197" s="41"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="49"/>
       <c r="B198" s="35" t="s">
         <v>786</v>
@@ -10478,7 +10494,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="49"/>
       <c r="B199" s="35" t="s">
         <v>1069</v>
@@ -10490,7 +10506,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="49"/>
       <c r="B200" s="35" t="s">
         <v>1071</v>
@@ -10500,7 +10516,7 @@
       </c>
       <c r="D200" s="41"/>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="49"/>
       <c r="B201" s="35" t="s">
         <v>1073</v>
@@ -10510,7 +10526,7 @@
       </c>
       <c r="D201" s="41"/>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="49"/>
       <c r="B202" s="35" t="s">
         <v>1076</v>
@@ -10520,7 +10536,7 @@
       </c>
       <c r="D202" s="41"/>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="49"/>
       <c r="B203" s="35" t="s">
         <v>799</v>
@@ -10530,7 +10546,7 @@
       </c>
       <c r="D203" s="41"/>
     </row>
-    <row r="204" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="49"/>
       <c r="B204" s="35" t="s">
         <v>797</v>
@@ -10540,7 +10556,7 @@
       </c>
       <c r="D204" s="41"/>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="49"/>
       <c r="B205" s="35" t="s">
         <v>827</v>
@@ -10550,7 +10566,7 @@
       </c>
       <c r="D205" s="41"/>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="49"/>
       <c r="B206" s="35" t="s">
         <v>1078</v>
@@ -10560,7 +10576,7 @@
       </c>
       <c r="D206" s="41"/>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="49"/>
       <c r="B207" s="35" t="s">
         <v>825</v>
@@ -10570,7 +10586,7 @@
       </c>
       <c r="D207" s="41"/>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="49"/>
       <c r="B208" s="35" t="s">
         <v>842</v>
@@ -10580,7 +10596,7 @@
       </c>
       <c r="D208" s="41"/>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="49"/>
       <c r="B209" s="35" t="s">
         <v>831</v>
@@ -10590,7 +10606,7 @@
       </c>
       <c r="D209" s="41"/>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="49"/>
       <c r="B210" s="35" t="s">
         <v>861</v>
@@ -10600,7 +10616,7 @@
       </c>
       <c r="D210" s="41"/>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="49"/>
       <c r="B211" s="35" t="s">
         <v>853</v>
@@ -10610,7 +10626,7 @@
       </c>
       <c r="D211" s="41"/>
     </row>
-    <row r="212" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="49"/>
       <c r="B212" s="35" t="s">
         <v>885</v>
@@ -10620,7 +10636,7 @@
       </c>
       <c r="D212" s="41"/>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="49"/>
       <c r="B213" s="35" t="s">
         <v>891</v>
@@ -10630,7 +10646,7 @@
       </c>
       <c r="D213" s="41"/>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="49"/>
       <c r="B214" s="35" t="s">
         <v>893</v>
@@ -10640,7 +10656,7 @@
       </c>
       <c r="D214" s="41"/>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="49"/>
       <c r="B215" s="35" t="s">
         <v>914</v>
@@ -10650,7 +10666,7 @@
       </c>
       <c r="D215" s="41"/>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="49"/>
       <c r="B216" s="35" t="s">
         <v>1080</v>
@@ -10662,7 +10678,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="49"/>
       <c r="B217" s="35" t="s">
         <v>889</v>
@@ -10672,7 +10688,7 @@
       </c>
       <c r="D217" s="41"/>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="49"/>
       <c r="B218" s="35" t="s">
         <v>977</v>
@@ -10682,7 +10698,7 @@
       </c>
       <c r="D218" s="41"/>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="49"/>
       <c r="B219" s="35" t="s">
         <v>244</v>
@@ -10694,7 +10710,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="49"/>
       <c r="B220" s="35" t="s">
         <v>1083</v>
@@ -10704,7 +10720,7 @@
       </c>
       <c r="D220" s="41"/>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="49"/>
       <c r="B221" s="35" t="s">
         <v>598</v>
@@ -10716,7 +10732,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A222" s="49"/>
       <c r="B222" s="35" t="s">
         <v>673</v>
@@ -10728,7 +10744,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="49"/>
       <c r="B223" s="35" t="s">
         <v>935</v>
@@ -10738,7 +10754,7 @@
       </c>
       <c r="D223" s="41"/>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="49"/>
       <c r="B224" s="35" t="s">
         <v>955</v>
@@ -10748,7 +10764,7 @@
       </c>
       <c r="D224" s="41"/>
     </row>
-    <row r="225" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="49"/>
       <c r="B225" s="35" t="s">
         <v>788</v>
@@ -10760,7 +10776,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="40" t="s">
         <v>1229</v>
       </c>
@@ -10775,7 +10791,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="49" t="s">
         <v>254</v>
       </c>
@@ -10787,7 +10803,7 @@
       </c>
       <c r="D227" s="41"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="49"/>
       <c r="B228" s="35" t="s">
         <v>257</v>
@@ -10797,7 +10813,7 @@
       </c>
       <c r="D228" s="41"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="49"/>
       <c r="B229" s="35" t="s">
         <v>627</v>
@@ -10807,7 +10823,7 @@
       </c>
       <c r="D229" s="41"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="49"/>
       <c r="B230" s="35" t="s">
         <v>259</v>
@@ -10817,7 +10833,7 @@
       </c>
       <c r="D230" s="41"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="49"/>
       <c r="B231" s="35" t="s">
         <v>261</v>
@@ -10827,7 +10843,7 @@
       </c>
       <c r="D231" s="41"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="40" t="s">
         <v>1217</v>
       </c>
@@ -10839,7 +10855,7 @@
       </c>
       <c r="D232" s="41"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="49" t="s">
         <v>1002</v>
       </c>
@@ -10851,7 +10867,7 @@
       </c>
       <c r="D233" s="41"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="49"/>
       <c r="B234" s="35" t="s">
         <v>1004</v>
@@ -10861,7 +10877,7 @@
       </c>
       <c r="D234" s="41"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="42" t="s">
         <v>794</v>
       </c>
@@ -10873,7 +10889,7 @@
       </c>
       <c r="D235" s="41"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="49" t="s">
         <v>263</v>
       </c>
@@ -10885,7 +10901,7 @@
       </c>
       <c r="D236" s="41"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="49"/>
       <c r="B237" s="35" t="s">
         <v>611</v>
@@ -10897,7 +10913,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="49"/>
       <c r="B238" s="35" t="s">
         <v>264</v>
@@ -10907,7 +10923,7 @@
       </c>
       <c r="D238" s="41"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="49"/>
       <c r="B239" s="35" t="s">
         <v>265</v>
@@ -10917,7 +10933,7 @@
       </c>
       <c r="D239" s="41"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="49"/>
       <c r="B240" s="35" t="s">
         <v>979</v>
@@ -10927,7 +10943,7 @@
       </c>
       <c r="D240" s="41"/>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="50" t="s">
         <v>846</v>
       </c>
@@ -10939,7 +10955,7 @@
       </c>
       <c r="D241" s="41"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="50"/>
       <c r="B242" s="35" t="s">
         <v>847</v>
@@ -10949,7 +10965,7 @@
       </c>
       <c r="D242" s="41"/>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="50"/>
       <c r="B243" s="35" t="s">
         <v>849</v>
@@ -10959,7 +10975,7 @@
       </c>
       <c r="D243" s="41"/>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="50"/>
       <c r="B244" s="35" t="s">
         <v>851</v>
@@ -10969,7 +10985,7 @@
       </c>
       <c r="D244" s="41"/>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="50"/>
       <c r="B245" s="35" t="s">
         <v>855</v>
@@ -10979,7 +10995,7 @@
       </c>
       <c r="D245" s="41"/>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="50"/>
       <c r="B246" s="35" t="s">
         <v>1085</v>
@@ -10989,7 +11005,7 @@
       </c>
       <c r="D246" s="41"/>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="50"/>
       <c r="B247" s="35" t="s">
         <v>1086</v>
@@ -10999,7 +11015,7 @@
       </c>
       <c r="D247" s="41"/>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="49" t="s">
         <v>707</v>
       </c>
@@ -11011,7 +11027,7 @@
       </c>
       <c r="D248" s="41"/>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="49"/>
       <c r="B249" s="35" t="s">
         <v>757</v>
@@ -11021,7 +11037,7 @@
       </c>
       <c r="D249" s="41"/>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="42" t="s">
         <v>266</v>
       </c>
@@ -11033,7 +11049,7 @@
       </c>
       <c r="D250" s="41"/>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A251" s="49" t="s">
         <v>269</v>
       </c>
@@ -11047,7 +11063,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="49"/>
       <c r="B252" s="35" t="s">
         <v>272</v>
@@ -11057,7 +11073,7 @@
       </c>
       <c r="D252" s="41"/>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="49" t="s">
         <v>275</v>
       </c>
@@ -11069,7 +11085,7 @@
       </c>
       <c r="D253" s="41"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="49"/>
       <c r="B254" s="35" t="s">
         <v>601</v>
@@ -11079,7 +11095,7 @@
       </c>
       <c r="D254" s="41"/>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="49"/>
       <c r="B255" s="35" t="s">
         <v>801</v>
@@ -11089,7 +11105,7 @@
       </c>
       <c r="D255" s="41"/>
     </row>
-    <row r="256" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A256" s="49" t="s">
         <v>276</v>
       </c>
@@ -11103,7 +11119,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="49"/>
       <c r="B257" s="35" t="s">
         <v>277</v>
@@ -11113,7 +11129,7 @@
       </c>
       <c r="D257" s="41"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="49"/>
       <c r="B258" s="35" t="s">
         <v>571</v>
@@ -11123,7 +11139,7 @@
       </c>
       <c r="D258" s="41"/>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="49"/>
       <c r="B259" s="35" t="s">
         <v>573</v>
@@ -11133,7 +11149,7 @@
       </c>
       <c r="D259" s="41"/>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="49"/>
       <c r="B260" s="35" t="s">
         <v>574</v>
@@ -11143,7 +11159,7 @@
       </c>
       <c r="D260" s="41"/>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="49"/>
       <c r="B261" s="35" t="s">
         <v>1175</v>
@@ -11153,7 +11169,7 @@
       </c>
       <c r="D261" s="41"/>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="49"/>
       <c r="B262" s="35" t="s">
         <v>279</v>
@@ -11163,7 +11179,7 @@
       </c>
       <c r="D262" s="41"/>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="49"/>
       <c r="B263" s="35" t="s">
         <v>770</v>
@@ -11173,7 +11189,7 @@
       </c>
       <c r="D263" s="41"/>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="49"/>
       <c r="B264" s="35" t="s">
         <v>937</v>
@@ -11183,7 +11199,7 @@
       </c>
       <c r="D264" s="41"/>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="49"/>
       <c r="B265" s="35" t="s">
         <v>1090</v>
@@ -11193,7 +11209,7 @@
       </c>
       <c r="D265" s="41"/>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="49" t="s">
         <v>282</v>
       </c>
@@ -11205,7 +11221,7 @@
       </c>
       <c r="D266" s="41"/>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="49"/>
       <c r="B267" s="35" t="s">
         <v>680</v>
@@ -11215,7 +11231,7 @@
       </c>
       <c r="D267" s="41"/>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="49"/>
       <c r="B268" s="35" t="s">
         <v>682</v>
@@ -11225,7 +11241,7 @@
       </c>
       <c r="D268" s="41"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="49"/>
       <c r="B269" s="35" t="s">
         <v>1176</v>
@@ -11235,7 +11251,7 @@
       </c>
       <c r="D269" s="41"/>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="49"/>
       <c r="B270" s="35" t="s">
         <v>753</v>
@@ -11245,7 +11261,7 @@
       </c>
       <c r="D270" s="41"/>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="49"/>
       <c r="B271" s="35" t="s">
         <v>759</v>
@@ -11255,7 +11271,7 @@
       </c>
       <c r="D271" s="41"/>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="49"/>
       <c r="B272" s="35" t="s">
         <v>779</v>
@@ -11265,7 +11281,7 @@
       </c>
       <c r="D272" s="41"/>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="49"/>
       <c r="B273" s="35" t="s">
         <v>804</v>
@@ -11275,7 +11291,7 @@
       </c>
       <c r="D273" s="41"/>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="49"/>
       <c r="B274" s="35" t="s">
         <v>805</v>
@@ -11285,7 +11301,7 @@
       </c>
       <c r="D274" s="41"/>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="49"/>
       <c r="B275" s="35" t="s">
         <v>1177</v>
@@ -11295,7 +11311,7 @@
       </c>
       <c r="D275" s="41"/>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="49"/>
       <c r="B276" s="35" t="s">
         <v>283</v>
@@ -11305,7 +11321,7 @@
       </c>
       <c r="D276" s="41"/>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="49"/>
       <c r="B277" s="35" t="s">
         <v>868</v>
@@ -11315,7 +11331,7 @@
       </c>
       <c r="D277" s="41"/>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="49"/>
       <c r="B278" s="35" t="s">
         <v>882</v>
@@ -11325,7 +11341,7 @@
       </c>
       <c r="D278" s="41"/>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="49"/>
       <c r="B279" s="35" t="s">
         <v>884</v>
@@ -11335,7 +11351,7 @@
       </c>
       <c r="D279" s="41"/>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="49"/>
       <c r="B280" s="35" t="s">
         <v>880</v>
@@ -11345,7 +11361,7 @@
       </c>
       <c r="D280" s="41"/>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="49"/>
       <c r="B281" s="35" t="s">
         <v>1091</v>
@@ -11355,7 +11371,7 @@
       </c>
       <c r="D281" s="41"/>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="49"/>
       <c r="B282" s="35" t="s">
         <v>284</v>
@@ -11365,7 +11381,7 @@
       </c>
       <c r="D282" s="41"/>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="49"/>
       <c r="B283" s="35" t="s">
         <v>949</v>
@@ -11375,7 +11391,7 @@
       </c>
       <c r="D283" s="41"/>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="49"/>
       <c r="B284" s="35" t="s">
         <v>991</v>
@@ -11385,7 +11401,7 @@
       </c>
       <c r="D284" s="41"/>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="49"/>
       <c r="B285" s="35" t="s">
         <v>990</v>
@@ -11395,7 +11411,7 @@
       </c>
       <c r="D285" s="41"/>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="49"/>
       <c r="B286" s="35" t="s">
         <v>1014</v>
@@ -11405,7 +11421,7 @@
       </c>
       <c r="D286" s="41"/>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="49" t="s">
         <v>286</v>
       </c>
@@ -11417,7 +11433,7 @@
       </c>
       <c r="D287" s="41"/>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="49"/>
       <c r="B288" s="35" t="s">
         <v>660</v>
@@ -11427,7 +11443,7 @@
       </c>
       <c r="D288" s="41"/>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="49"/>
       <c r="B289" s="35" t="s">
         <v>662</v>
@@ -11437,7 +11453,7 @@
       </c>
       <c r="D289" s="41"/>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="49"/>
       <c r="B290" s="35" t="s">
         <v>813</v>
@@ -11449,7 +11465,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="49"/>
       <c r="B291" s="35" t="s">
         <v>815</v>
@@ -11459,7 +11475,7 @@
       </c>
       <c r="D291" s="41"/>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="49"/>
       <c r="B292" s="35" t="s">
         <v>817</v>
@@ -11471,7 +11487,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="49"/>
       <c r="B293" s="35" t="s">
         <v>820</v>
@@ -11483,7 +11499,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="49"/>
       <c r="B294" s="35" t="s">
         <v>823</v>
@@ -11495,7 +11511,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A295" s="49"/>
       <c r="B295" s="35" t="s">
         <v>863</v>
@@ -11507,7 +11523,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="49"/>
       <c r="B296" s="35" t="s">
         <v>287</v>
@@ -11517,7 +11533,7 @@
       </c>
       <c r="D296" s="41"/>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="49" t="s">
         <v>663</v>
       </c>
@@ -11529,7 +11545,7 @@
       </c>
       <c r="D297" s="41"/>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="49"/>
       <c r="B298" s="35" t="s">
         <v>1092</v>
@@ -11539,7 +11555,7 @@
       </c>
       <c r="D298" s="41"/>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="49"/>
       <c r="B299" s="35" t="s">
         <v>1093</v>
@@ -11549,7 +11565,7 @@
       </c>
       <c r="D299" s="41"/>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="49"/>
       <c r="B300" s="35" t="s">
         <v>968</v>
@@ -11559,7 +11575,7 @@
       </c>
       <c r="D300" s="41"/>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="49"/>
       <c r="B301" s="35" t="s">
         <v>986</v>
@@ -11569,7 +11585,7 @@
       </c>
       <c r="D301" s="41"/>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="49"/>
       <c r="B302" s="35" t="s">
         <v>1094</v>
@@ -11579,7 +11595,7 @@
       </c>
       <c r="D302" s="41"/>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A303" s="49" t="s">
         <v>565</v>
       </c>
@@ -11593,7 +11609,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="49"/>
       <c r="B304" s="35" t="s">
         <v>641</v>
@@ -11603,7 +11619,7 @@
       </c>
       <c r="D304" s="41"/>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="49"/>
       <c r="B305" s="35" t="s">
         <v>723</v>
@@ -11613,7 +11629,7 @@
       </c>
       <c r="D305" s="43"/>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="49"/>
       <c r="B306" s="35" t="s">
         <v>745</v>
@@ -11623,7 +11639,7 @@
       </c>
       <c r="D306" s="43"/>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="49"/>
       <c r="B307" s="35" t="s">
         <v>742</v>
@@ -11633,7 +11649,7 @@
       </c>
       <c r="D307" s="43"/>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="49"/>
       <c r="B308" s="35" t="s">
         <v>743</v>
@@ -11643,7 +11659,7 @@
       </c>
       <c r="D308" s="43"/>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="49"/>
       <c r="B309" s="35" t="s">
         <v>744</v>
@@ -11653,7 +11669,7 @@
       </c>
       <c r="D309" s="43"/>
     </row>
-    <row r="310" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A310" s="49"/>
       <c r="B310" s="35" t="s">
         <v>643</v>
@@ -11665,7 +11681,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="49"/>
       <c r="B311" s="35" t="s">
         <v>1095</v>
@@ -11675,7 +11691,7 @@
       </c>
       <c r="D311" s="43"/>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="49"/>
       <c r="B312" s="35" t="s">
         <v>997</v>
@@ -11685,7 +11701,7 @@
       </c>
       <c r="D312" s="43"/>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="42" t="s">
         <v>837</v>
       </c>
@@ -11697,7 +11713,7 @@
       </c>
       <c r="D313" s="43"/>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="42" t="s">
         <v>1011</v>
       </c>
@@ -11709,7 +11725,7 @@
       </c>
       <c r="D314" s="41"/>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="49" t="s">
         <v>648</v>
       </c>
@@ -11721,7 +11737,7 @@
       </c>
       <c r="D315" s="41"/>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="49"/>
       <c r="B316" s="35" t="s">
         <v>1099</v>
@@ -11731,7 +11747,7 @@
       </c>
       <c r="D316" s="41"/>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="49"/>
       <c r="B317" s="35" t="s">
         <v>649</v>
@@ -11741,7 +11757,7 @@
       </c>
       <c r="D317" s="41"/>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="49"/>
       <c r="B318" s="35" t="s">
         <v>807</v>
@@ -11751,7 +11767,7 @@
       </c>
       <c r="D318" s="41"/>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="49"/>
       <c r="B319" s="35" t="s">
         <v>947</v>
@@ -11761,7 +11777,7 @@
       </c>
       <c r="D319" s="41"/>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="49" t="s">
         <v>754</v>
       </c>
@@ -11773,7 +11789,7 @@
       </c>
       <c r="D320" s="43"/>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="49"/>
       <c r="B321" s="35" t="s">
         <v>843</v>
@@ -11783,7 +11799,7 @@
       </c>
       <c r="D321" s="43"/>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="42" t="s">
         <v>867</v>
       </c>
@@ -11795,7 +11811,7 @@
       </c>
       <c r="D322" s="43"/>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="42" t="s">
         <v>1178</v>
       </c>
@@ -11807,7 +11823,7 @@
       </c>
       <c r="D323" s="43"/>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="42" t="s">
         <v>289</v>
       </c>
@@ -11819,7 +11835,7 @@
       </c>
       <c r="D324" s="41"/>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="49" t="s">
         <v>291</v>
       </c>
@@ -11831,7 +11847,7 @@
       </c>
       <c r="D325" s="41"/>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="49"/>
       <c r="B326" s="35" t="s">
         <v>294</v>
@@ -11841,7 +11857,7 @@
       </c>
       <c r="D326" s="41"/>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="49"/>
       <c r="B327" s="35" t="s">
         <v>1232</v>
@@ -11851,7 +11867,7 @@
       </c>
       <c r="D327" s="41"/>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="49"/>
       <c r="B328" s="35" t="s">
         <v>295</v>
@@ -11861,7 +11877,7 @@
       </c>
       <c r="D328" s="41"/>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="42" t="s">
         <v>993</v>
       </c>
@@ -11873,7 +11889,7 @@
       </c>
       <c r="D329" s="41"/>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="49" t="s">
         <v>296</v>
       </c>
@@ -11885,7 +11901,7 @@
       </c>
       <c r="D330" s="41"/>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="49"/>
       <c r="B331" s="35" t="s">
         <v>838</v>
@@ -11895,7 +11911,7 @@
       </c>
       <c r="D331" s="41"/>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="49"/>
       <c r="B332" s="35" t="s">
         <v>917</v>
@@ -11905,7 +11921,7 @@
       </c>
       <c r="D332" s="41"/>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="49"/>
       <c r="B333" s="35" t="s">
         <v>297</v>
@@ -11915,7 +11931,7 @@
       </c>
       <c r="D333" s="41"/>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="49"/>
       <c r="B334" s="35" t="s">
         <v>298</v>
@@ -11925,7 +11941,7 @@
       </c>
       <c r="D334" s="41"/>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="40" t="s">
         <v>1181</v>
       </c>
@@ -11937,7 +11953,7 @@
       </c>
       <c r="D335" s="41"/>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="42" t="s">
         <v>906</v>
       </c>
@@ -11949,7 +11965,7 @@
       </c>
       <c r="D336" s="41"/>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="49" t="s">
         <v>300</v>
       </c>
@@ -11961,7 +11977,7 @@
       </c>
       <c r="D337" s="41"/>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="49"/>
       <c r="B338" s="35" t="s">
         <v>1101</v>
@@ -11971,7 +11987,7 @@
       </c>
       <c r="D338" s="41"/>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="49"/>
       <c r="B339" s="35" t="s">
         <v>910</v>
@@ -11981,7 +11997,7 @@
       </c>
       <c r="D339" s="41"/>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="49"/>
       <c r="B340" s="35" t="s">
         <v>1102</v>
@@ -11991,7 +12007,7 @@
       </c>
       <c r="D340" s="41"/>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="49"/>
       <c r="B341" s="35" t="s">
         <v>915</v>
@@ -12001,7 +12017,7 @@
       </c>
       <c r="D341" s="41"/>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="49"/>
       <c r="B342" s="35" t="s">
         <v>911</v>
@@ -12011,7 +12027,7 @@
       </c>
       <c r="D342" s="41"/>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="49"/>
       <c r="B343" s="35" t="s">
         <v>1103</v>
@@ -12021,7 +12037,7 @@
       </c>
       <c r="D343" s="41"/>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="49"/>
       <c r="B344" s="35" t="s">
         <v>912</v>
@@ -12031,7 +12047,7 @@
       </c>
       <c r="D344" s="41"/>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="49"/>
       <c r="B345" s="35" t="s">
         <v>913</v>
@@ -12041,7 +12057,7 @@
       </c>
       <c r="D345" s="41"/>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="49"/>
       <c r="B346" s="35" t="s">
         <v>301</v>
@@ -12051,7 +12067,7 @@
       </c>
       <c r="D346" s="41"/>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="49" t="s">
         <v>617</v>
       </c>
@@ -12063,7 +12079,7 @@
       </c>
       <c r="D347" s="41"/>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="49"/>
       <c r="B348" s="35" t="s">
         <v>302</v>
@@ -12073,7 +12089,7 @@
       </c>
       <c r="D348" s="41"/>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="49" t="s">
         <v>616</v>
       </c>
@@ -12085,7 +12101,7 @@
       </c>
       <c r="D349" s="41"/>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="49"/>
       <c r="B350" s="35" t="s">
         <v>618</v>
@@ -12095,7 +12111,7 @@
       </c>
       <c r="D350" s="41"/>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="49"/>
       <c r="B351" s="35" t="s">
         <v>619</v>
@@ -12105,7 +12121,7 @@
       </c>
       <c r="D351" s="41"/>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="49"/>
       <c r="B352" s="35" t="s">
         <v>995</v>
@@ -12115,7 +12131,7 @@
       </c>
       <c r="D352" s="41"/>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="42" t="s">
         <v>944</v>
       </c>
@@ -12127,7 +12143,7 @@
       </c>
       <c r="D353" s="41"/>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="42" t="s">
         <v>932</v>
       </c>
@@ -12139,7 +12155,7 @@
       </c>
       <c r="D354" s="41"/>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="49" t="s">
         <v>304</v>
       </c>
@@ -12151,7 +12167,7 @@
       </c>
       <c r="D355" s="41"/>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="49"/>
       <c r="B356" s="35" t="s">
         <v>305</v>
@@ -12161,7 +12177,7 @@
       </c>
       <c r="D356" s="41"/>
     </row>
-    <row r="357" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A357" s="49"/>
       <c r="B357" s="35" t="s">
         <v>651</v>
@@ -12173,7 +12189,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="42" t="s">
         <v>655</v>
       </c>
@@ -12185,7 +12201,7 @@
       </c>
       <c r="D358" s="41"/>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="49" t="s">
         <v>307</v>
       </c>
@@ -12197,7 +12213,7 @@
       </c>
       <c r="D359" s="41"/>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="49"/>
       <c r="B360" s="35" t="s">
         <v>543</v>
@@ -12207,7 +12223,7 @@
       </c>
       <c r="D360" s="41"/>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="49"/>
       <c r="B361" s="35" t="s">
         <v>771</v>
@@ -12217,7 +12233,7 @@
       </c>
       <c r="D361" s="41"/>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="49"/>
       <c r="B362" s="35" t="s">
         <v>772</v>
@@ -12227,7 +12243,7 @@
       </c>
       <c r="D362" s="41"/>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="49"/>
       <c r="B363" s="35" t="s">
         <v>629</v>
@@ -12237,7 +12253,7 @@
       </c>
       <c r="D363" s="41"/>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="49"/>
       <c r="B364" s="35" t="s">
         <v>308</v>
@@ -12247,7 +12263,7 @@
       </c>
       <c r="D364" s="41"/>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="49"/>
       <c r="B365" s="35" t="s">
         <v>631</v>
@@ -12257,7 +12273,7 @@
       </c>
       <c r="D365" s="41"/>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="49"/>
       <c r="B366" s="35" t="s">
         <v>632</v>
@@ -12269,7 +12285,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="49"/>
       <c r="B367" s="35" t="s">
         <v>750</v>
@@ -12279,7 +12295,7 @@
       </c>
       <c r="D367" s="41"/>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="49"/>
       <c r="B368" s="35" t="s">
         <v>310</v>
@@ -12289,7 +12305,7 @@
       </c>
       <c r="D368" s="41"/>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="49"/>
       <c r="B369" s="35" t="s">
         <v>780</v>
@@ -12299,7 +12315,7 @@
       </c>
       <c r="D369" s="41"/>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="49"/>
       <c r="B370" s="35" t="s">
         <v>791</v>
@@ -12309,7 +12325,7 @@
       </c>
       <c r="D370" s="41"/>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="49"/>
       <c r="B371" s="35" t="s">
         <v>1108</v>
@@ -12319,7 +12335,7 @@
       </c>
       <c r="D371" s="41"/>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="49"/>
       <c r="B372" s="35" t="s">
         <v>840</v>
@@ -12329,7 +12345,7 @@
       </c>
       <c r="D372" s="41"/>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="49"/>
       <c r="B373" s="35" t="s">
         <v>897</v>
@@ -12339,7 +12355,7 @@
       </c>
       <c r="D373" s="41"/>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="49"/>
       <c r="B374" s="35" t="s">
         <v>870</v>
@@ -12349,7 +12365,7 @@
       </c>
       <c r="D374" s="41"/>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="49"/>
       <c r="B375" s="35" t="s">
         <v>898</v>
@@ -12359,7 +12375,7 @@
       </c>
       <c r="D375" s="41"/>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="49"/>
       <c r="B376" s="35" t="s">
         <v>900</v>
@@ -12369,7 +12385,7 @@
       </c>
       <c r="D376" s="41"/>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="49"/>
       <c r="B377" s="35" t="s">
         <v>901</v>
@@ -12379,7 +12395,7 @@
       </c>
       <c r="D377" s="41"/>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="49"/>
       <c r="B378" s="35" t="s">
         <v>1110</v>
@@ -12389,7 +12405,7 @@
       </c>
       <c r="D378" s="41"/>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="49"/>
       <c r="B379" s="35" t="s">
         <v>902</v>
@@ -12399,7 +12415,7 @@
       </c>
       <c r="D379" s="41"/>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="49"/>
       <c r="B380" s="35" t="s">
         <v>903</v>
@@ -12409,7 +12425,7 @@
       </c>
       <c r="D380" s="41"/>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A381" s="49"/>
       <c r="B381" s="35" t="s">
         <v>904</v>
@@ -12421,7 +12437,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="49"/>
       <c r="B382" s="35" t="s">
         <v>905</v>
@@ -12431,7 +12447,7 @@
       </c>
       <c r="D382" s="41"/>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="49"/>
       <c r="B383" s="35" t="s">
         <v>930</v>
@@ -12441,7 +12457,7 @@
       </c>
       <c r="D383" s="41"/>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="49"/>
       <c r="B384" s="35" t="s">
         <v>312</v>
@@ -12451,7 +12467,7 @@
       </c>
       <c r="D384" s="41"/>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="49"/>
       <c r="B385" s="35" t="s">
         <v>931</v>
@@ -12461,7 +12477,7 @@
       </c>
       <c r="D385" s="41"/>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="49"/>
       <c r="B386" s="35" t="s">
         <v>928</v>
@@ -12471,7 +12487,7 @@
       </c>
       <c r="D386" s="41"/>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="49"/>
       <c r="B387" s="35" t="s">
         <v>939</v>
@@ -12481,7 +12497,7 @@
       </c>
       <c r="D387" s="41"/>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="49"/>
       <c r="B388" s="35" t="s">
         <v>313</v>
@@ -12493,7 +12509,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="49" t="s">
         <v>593</v>
       </c>
@@ -12505,7 +12521,7 @@
       </c>
       <c r="D389" s="41"/>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="49"/>
       <c r="B390" s="35" t="s">
         <v>1112</v>
@@ -12515,7 +12531,7 @@
       </c>
       <c r="D390" s="41"/>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="49"/>
       <c r="B391" s="35" t="s">
         <v>1021</v>
@@ -12525,7 +12541,7 @@
       </c>
       <c r="D391" s="41"/>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="49"/>
       <c r="B392" s="35" t="s">
         <v>1023</v>
@@ -12535,7 +12551,7 @@
       </c>
       <c r="D392" s="41"/>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="49" t="s">
         <v>669</v>
       </c>
@@ -12547,7 +12563,7 @@
       </c>
       <c r="D393" s="41"/>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="49"/>
       <c r="B394" s="35" t="s">
         <v>670</v>
@@ -12557,7 +12573,7 @@
       </c>
       <c r="D394" s="41"/>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="49"/>
       <c r="B395" s="35" t="s">
         <v>1114</v>
@@ -12567,7 +12583,7 @@
       </c>
       <c r="D395" s="41"/>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="49"/>
       <c r="B396" s="35" t="s">
         <v>671</v>
@@ -12579,7 +12595,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="49"/>
       <c r="B397" s="35" t="s">
         <v>761</v>
@@ -12589,7 +12605,7 @@
       </c>
       <c r="D397" s="41"/>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="49"/>
       <c r="B398" s="35" t="s">
         <v>919</v>
@@ -12599,7 +12615,7 @@
       </c>
       <c r="D398" s="41"/>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="49"/>
       <c r="B399" s="35" t="s">
         <v>1015</v>
@@ -12609,7 +12625,7 @@
       </c>
       <c r="D399" s="41"/>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="49"/>
       <c r="B400" s="35" t="s">
         <v>1024</v>
@@ -12619,7 +12635,7 @@
       </c>
       <c r="D400" s="41"/>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="49" t="s">
         <v>315</v>
       </c>
@@ -12631,7 +12647,7 @@
       </c>
       <c r="D401" s="41"/>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A402" s="49"/>
       <c r="B402" s="35" t="s">
         <v>1115</v>
@@ -12643,7 +12659,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="49"/>
       <c r="B403" s="35" t="s">
         <v>316</v>
@@ -12653,7 +12669,7 @@
       </c>
       <c r="D403" s="41"/>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="49"/>
       <c r="B404" s="35" t="s">
         <v>1116</v>
@@ -12663,7 +12679,7 @@
       </c>
       <c r="D404" s="41"/>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="49"/>
       <c r="B405" s="35" t="s">
         <v>1118</v>
@@ -12673,7 +12689,7 @@
       </c>
       <c r="D405" s="41"/>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="49"/>
       <c r="B406" s="35" t="s">
         <v>635</v>
@@ -12683,7 +12699,7 @@
       </c>
       <c r="D406" s="41"/>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="49"/>
       <c r="B407" s="35" t="s">
         <v>636</v>
@@ -12693,7 +12709,7 @@
       </c>
       <c r="D407" s="41"/>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="49"/>
       <c r="B408" s="35" t="s">
         <v>833</v>
@@ -12703,7 +12719,7 @@
       </c>
       <c r="D408" s="41"/>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="49"/>
       <c r="B409" s="35" t="s">
         <v>834</v>
@@ -12713,7 +12729,7 @@
       </c>
       <c r="D409" s="41"/>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="49"/>
       <c r="B410" s="35" t="s">
         <v>1119</v>
@@ -12723,7 +12739,7 @@
       </c>
       <c r="D410" s="41"/>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="49"/>
       <c r="B411" s="35" t="s">
         <v>953</v>
@@ -12733,7 +12749,7 @@
       </c>
       <c r="D411" s="41"/>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="49"/>
       <c r="B412" s="35" t="s">
         <v>317</v>
@@ -12743,7 +12759,7 @@
       </c>
       <c r="D412" s="41"/>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="49"/>
       <c r="B413" s="35" t="s">
         <v>964</v>
@@ -12753,7 +12769,7 @@
       </c>
       <c r="D413" s="41"/>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="49"/>
       <c r="B414" s="35" t="s">
         <v>318</v>
@@ -12763,7 +12779,7 @@
       </c>
       <c r="D414" s="41"/>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="49"/>
       <c r="B415" s="35" t="s">
         <v>320</v>
@@ -12773,7 +12789,7 @@
       </c>
       <c r="D415" s="41"/>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="49" t="s">
         <v>871</v>
       </c>
@@ -12785,7 +12801,7 @@
       </c>
       <c r="D416" s="41"/>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="49"/>
       <c r="B417" s="35" t="s">
         <v>1121</v>
@@ -12793,7 +12809,7 @@
       <c r="C417" s="36"/>
       <c r="D417" s="41"/>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="49"/>
       <c r="B418" s="35" t="s">
         <v>1122</v>
@@ -12803,7 +12819,7 @@
       </c>
       <c r="D418" s="41"/>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="49"/>
       <c r="B419" s="35" t="s">
         <v>872</v>
@@ -12813,7 +12829,7 @@
       </c>
       <c r="D419" s="41"/>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="42" t="s">
         <v>952</v>
       </c>
@@ -12825,7 +12841,7 @@
       </c>
       <c r="D420" s="41"/>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="49" t="s">
         <v>971</v>
       </c>
@@ -12837,7 +12853,7 @@
       </c>
       <c r="D421" s="41"/>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="49"/>
       <c r="B422" s="35" t="s">
         <v>972</v>
@@ -12847,7 +12863,7 @@
       </c>
       <c r="D422" s="41"/>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="49" t="s">
         <v>322</v>
       </c>
@@ -12859,7 +12875,7 @@
       </c>
       <c r="D423" s="41"/>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="49"/>
       <c r="B424" s="35" t="s">
         <v>637</v>
@@ -12869,7 +12885,7 @@
       </c>
       <c r="D424" s="41"/>
     </row>
-    <row r="425" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A425" s="49"/>
       <c r="B425" s="35" t="s">
         <v>324</v>
@@ -12881,7 +12897,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="49"/>
       <c r="B426" s="35" t="s">
         <v>924</v>
@@ -12891,7 +12907,7 @@
       </c>
       <c r="D426" s="41"/>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="49"/>
       <c r="B427" s="35" t="s">
         <v>954</v>
@@ -12901,7 +12917,7 @@
       </c>
       <c r="D427" s="41"/>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="49"/>
       <c r="B428" s="35" t="s">
         <v>639</v>
@@ -12911,7 +12927,7 @@
       </c>
       <c r="D428" s="41"/>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="49"/>
       <c r="B429" s="35" t="s">
         <v>966</v>
@@ -12921,7 +12937,7 @@
       </c>
       <c r="D429" s="41"/>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="49" t="s">
         <v>326</v>
       </c>
@@ -12933,7 +12949,7 @@
       </c>
       <c r="D430" s="41"/>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="49"/>
       <c r="B431" s="35" t="s">
         <v>690</v>
@@ -12943,7 +12959,7 @@
       </c>
       <c r="D431" s="41"/>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="49"/>
       <c r="B432" s="35" t="s">
         <v>691</v>
@@ -12953,7 +12969,7 @@
       </c>
       <c r="D432" s="41"/>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="49"/>
       <c r="B433" s="35" t="s">
         <v>739</v>
@@ -12963,7 +12979,7 @@
       </c>
       <c r="D433" s="41"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="49"/>
       <c r="B434" s="35" t="s">
         <v>327</v>
@@ -12975,7 +12991,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="49"/>
       <c r="B435" s="35" t="s">
         <v>835</v>
@@ -12985,7 +13001,7 @@
       </c>
       <c r="D435" s="41"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="49"/>
       <c r="B436" s="35" t="s">
         <v>1026</v>
@@ -12995,7 +13011,7 @@
       </c>
       <c r="D436" s="41"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="49"/>
       <c r="B437" s="35" t="s">
         <v>1124</v>
@@ -13005,7 +13021,7 @@
       </c>
       <c r="D437" s="41"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="49"/>
       <c r="B438" s="35" t="s">
         <v>1000</v>
@@ -13015,7 +13031,7 @@
       </c>
       <c r="D438" s="41"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="49" t="s">
         <v>329</v>
       </c>
@@ -13027,7 +13043,7 @@
       </c>
       <c r="D439" s="41"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="49"/>
       <c r="B440" s="35" t="s">
         <v>806</v>
@@ -13037,7 +13053,7 @@
       </c>
       <c r="D440" s="41"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="49"/>
       <c r="B441" s="35" t="s">
         <v>909</v>
@@ -13047,7 +13063,7 @@
       </c>
       <c r="D441" s="41"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="49"/>
       <c r="B442" s="35" t="s">
         <v>774</v>
@@ -13057,7 +13073,7 @@
       </c>
       <c r="D442" s="41"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="49"/>
       <c r="B443" s="35" t="s">
         <v>1183</v>
@@ -13067,7 +13083,7 @@
       </c>
       <c r="D443" s="41"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="49" t="s">
         <v>331</v>
       </c>
@@ -13079,7 +13095,7 @@
       </c>
       <c r="D444" s="41"/>
     </row>
-    <row r="445" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A445" s="49"/>
       <c r="B445" s="35" t="s">
         <v>334</v>
@@ -13091,7 +13107,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="49"/>
       <c r="B446" s="35" t="s">
         <v>1008</v>
@@ -13104,7 +13120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="45" t="s">
         <v>1007</v>
       </c>
@@ -13121,6 +13137,47 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="A421:A422"/>
+    <mergeCell ref="A423:A429"/>
+    <mergeCell ref="A430:A438"/>
+    <mergeCell ref="A444:A446"/>
+    <mergeCell ref="A439:A443"/>
+    <mergeCell ref="A416:A419"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="A325:A328"/>
+    <mergeCell ref="A330:A334"/>
+    <mergeCell ref="A337:A346"/>
+    <mergeCell ref="A347:A348"/>
+    <mergeCell ref="A349:A352"/>
+    <mergeCell ref="A355:A357"/>
+    <mergeCell ref="A359:A388"/>
+    <mergeCell ref="A389:A392"/>
+    <mergeCell ref="A393:A400"/>
+    <mergeCell ref="A401:A415"/>
+    <mergeCell ref="A315:A319"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A236:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A253:A255"/>
+    <mergeCell ref="A256:A265"/>
+    <mergeCell ref="A266:A286"/>
+    <mergeCell ref="A287:A296"/>
+    <mergeCell ref="A297:A302"/>
+    <mergeCell ref="A303:A312"/>
+    <mergeCell ref="A227:A231"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A116:A120"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A123:A127"/>
+    <mergeCell ref="A128:A134"/>
+    <mergeCell ref="A135:A140"/>
+    <mergeCell ref="A142:A156"/>
+    <mergeCell ref="A157:A225"/>
     <mergeCell ref="A98:A100"/>
     <mergeCell ref="A2:A10"/>
     <mergeCell ref="A12:A13"/>
@@ -13134,49 +13191,43 @@
     <mergeCell ref="A93:A94"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A227:A231"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A116:A120"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="A123:A127"/>
-    <mergeCell ref="A128:A134"/>
-    <mergeCell ref="A135:A140"/>
-    <mergeCell ref="A142:A156"/>
-    <mergeCell ref="A157:A225"/>
-    <mergeCell ref="A315:A319"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A236:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A253:A255"/>
-    <mergeCell ref="A256:A265"/>
-    <mergeCell ref="A266:A286"/>
-    <mergeCell ref="A287:A296"/>
-    <mergeCell ref="A297:A302"/>
-    <mergeCell ref="A303:A312"/>
-    <mergeCell ref="A416:A419"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="A325:A328"/>
-    <mergeCell ref="A330:A334"/>
-    <mergeCell ref="A337:A346"/>
-    <mergeCell ref="A347:A348"/>
-    <mergeCell ref="A349:A352"/>
-    <mergeCell ref="A355:A357"/>
-    <mergeCell ref="A359:A388"/>
-    <mergeCell ref="A389:A392"/>
-    <mergeCell ref="A393:A400"/>
-    <mergeCell ref="A401:A415"/>
-    <mergeCell ref="A421:A422"/>
-    <mergeCell ref="A423:A429"/>
-    <mergeCell ref="A430:A438"/>
-    <mergeCell ref="A444:A446"/>
-    <mergeCell ref="A439:A443"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ED38CF-7EC4-46DC-ADBE-6722248DB9E3}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>